--- a/tinHelm/excel/Event.xlsx
+++ b/tinHelm/excel/Event.xlsx
@@ -1094,7 +1094,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1">
-        <v>4001</v>
+        <v>1</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>10</v>
@@ -1105,7 +1105,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="1">
-        <v>4002</v>
+        <v>2</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>12</v>
@@ -1116,7 +1116,7 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="1">
-        <v>4003</v>
+        <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>14</v>
@@ -1127,7 +1127,7 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="1">
-        <v>4004</v>
+        <v>4</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>16</v>
@@ -1176,7 +1176,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1">
-        <v>4001</v>
+        <v>1</v>
       </c>
       <c r="B1" t="s">
         <v>18</v>
@@ -1184,7 +1184,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1">
-        <v>4002</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
@@ -1192,7 +1192,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1">
-        <v>4003</v>
+        <v>3</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
@@ -1200,7 +1200,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1">
-        <v>4004</v>
+        <v>4</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
